--- a/Data/EXCEL/Transfer/salemon/202206/6580-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6580-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5EED068-ACFE-47C2-98EA-ED4B98B42A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38FA607C-8E6A-40E7-B299-D302E09FD62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6580-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1218,22 +1218,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="8" width="12.25" customWidth="1"/>
-    <col min="9" max="9" width="10.25" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="11" width="12.25" customWidth="1"/>
-    <col min="12" max="12" width="10.75" customWidth="1"/>
-    <col min="13" max="13" width="12.25" customWidth="1"/>
-    <col min="14" max="14" width="10.25" customWidth="1"/>
-    <col min="15" max="15" width="10.75" customWidth="1"/>
-    <col min="16" max="16" width="12.25" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="11.125" customWidth="1"/>
+    <col min="10" max="10" width="11.75" customWidth="1"/>
+    <col min="11" max="11" width="13.375" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="14" max="14" width="11.125" customWidth="1"/>
+    <col min="15" max="15" width="11.75" customWidth="1"/>
+    <col min="16" max="16" width="13.375" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1386,31 +1386,31 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>38.85</v>
+        <v>33.5</v>
       </c>
       <c r="C5" s="7">
-        <v>33.5</v>
+        <v>31.95</v>
       </c>
       <c r="D5" s="7">
-        <v>39.200000000000003</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="E5" s="7">
-        <v>32.5</v>
+        <v>30.9</v>
       </c>
       <c r="F5" s="8">
-        <v>-5.35</v>
+        <v>-1.55</v>
       </c>
       <c r="G5" s="8">
-        <v>-13.77</v>
+        <v>-4.63</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
       </c>
-      <c r="I5" s="8">
-        <v>-100</v>
+      <c r="I5" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>17</v>
@@ -1424,8 +1424,8 @@
       <c r="M5" s="9">
         <v>0</v>
       </c>
-      <c r="N5" s="8">
-        <v>-100</v>
+      <c r="N5" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>17</v>
@@ -1439,31 +1439,31 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
         <v>38.85</v>
       </c>
       <c r="C6" s="7">
-        <v>38.85</v>
+        <v>33.5</v>
       </c>
       <c r="D6" s="7">
-        <v>41</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="E6" s="7">
-        <v>37.4</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
+        <v>32.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>-5.35</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-13.77</v>
       </c>
       <c r="H6" s="9">
-        <v>2.9999999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="I6" s="8">
-        <v>-95.2</v>
+        <v>-100</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>17</v>
@@ -1475,10 +1475,10 @@
         <v>17</v>
       </c>
       <c r="M6" s="9">
-        <v>2.9999999999999997E-4</v>
+        <v>0</v>
       </c>
       <c r="N6" s="8">
-        <v>-95.2</v>
+        <v>-100</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>17</v>
@@ -1492,52 +1492,52 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>40.200000000000003</v>
+        <v>38.85</v>
       </c>
       <c r="C7" s="7">
         <v>38.85</v>
       </c>
       <c r="D7" s="7">
-        <v>44.35</v>
+        <v>41</v>
       </c>
       <c r="E7" s="7">
-        <v>35</v>
-      </c>
-      <c r="F7" s="8">
-        <v>-1.35</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-3.36</v>
+        <v>37.4</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
       </c>
       <c r="H7" s="9">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>17</v>
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I7" s="8">
+        <v>-95.2</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="9">
-        <v>5.8999999999999999E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M7" s="9">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>17</v>
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="N7" s="8">
+        <v>-95.2</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="9">
-        <v>5.8999999999999999E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>17</v>
@@ -1545,28 +1545,28 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>80</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="C8" s="7">
-        <v>40.200000000000003</v>
+        <v>38.85</v>
       </c>
       <c r="D8" s="7">
-        <v>89.5</v>
+        <v>44.35</v>
       </c>
       <c r="E8" s="7">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F8" s="8">
-        <v>-39.799999999999997</v>
+        <v>-1.35</v>
       </c>
       <c r="G8" s="8">
-        <v>-49.75</v>
+        <v>-3.36</v>
       </c>
       <c r="H8" s="9">
-        <v>0</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>17</v>
@@ -1575,13 +1575,13 @@
         <v>17</v>
       </c>
       <c r="K8" s="9">
-        <v>0</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M8" s="9">
-        <v>0</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>17</v>
@@ -1590,7 +1590,7 @@
         <v>17</v>
       </c>
       <c r="P8" s="9">
-        <v>0</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>17</v>
@@ -1598,31 +1598,31 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>53.9</v>
+        <v>80</v>
       </c>
       <c r="C9" s="7">
-        <v>80</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="D9" s="7">
-        <v>84.5</v>
+        <v>89.5</v>
       </c>
       <c r="E9" s="7">
-        <v>51</v>
-      </c>
-      <c r="F9" s="10">
-        <v>26.1</v>
-      </c>
-      <c r="G9" s="10">
-        <v>48.42</v>
+        <v>30</v>
+      </c>
+      <c r="F9" s="8">
+        <v>-39.799999999999997</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-49.75</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
       </c>
-      <c r="I9" s="8">
-        <v>-100</v>
+      <c r="I9" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>17</v>
@@ -1636,8 +1636,8 @@
       <c r="M9" s="9">
         <v>0</v>
       </c>
-      <c r="N9" s="8">
-        <v>-100</v>
+      <c r="N9" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>17</v>
@@ -1651,137 +1651,137 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>30.6</v>
+        <v>53.9</v>
       </c>
       <c r="C10" s="7">
-        <v>53.9</v>
+        <v>80</v>
       </c>
       <c r="D10" s="7">
-        <v>60.9</v>
+        <v>84.5</v>
       </c>
       <c r="E10" s="7">
-        <v>30.05</v>
+        <v>51</v>
       </c>
       <c r="F10" s="10">
-        <v>23.3</v>
+        <v>26.1</v>
       </c>
       <c r="G10" s="10">
-        <v>76.14</v>
+        <v>48.42</v>
       </c>
       <c r="H10" s="9">
-        <v>3.4099999999999998E-2</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="10">
-        <v>1.57</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K10" s="9">
-        <v>5.1400000000000001E-2</v>
-      </c>
-      <c r="L10" s="10">
-        <v>53</v>
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M10" s="9">
-        <v>3.4099999999999998E-2</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O10" s="10">
-        <v>1.57</v>
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P10" s="9">
-        <v>5.1400000000000001E-2</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>53</v>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>29.7</v>
+        <v>30.6</v>
       </c>
       <c r="C11" s="7">
-        <v>30.6</v>
+        <v>53.9</v>
       </c>
       <c r="D11" s="7">
-        <v>33.5</v>
+        <v>60.9</v>
       </c>
       <c r="E11" s="7">
-        <v>28.5</v>
+        <v>30.05</v>
       </c>
       <c r="F11" s="10">
-        <v>0.9</v>
+        <v>23.3</v>
       </c>
       <c r="G11" s="10">
-        <v>3.03</v>
+        <v>76.14</v>
       </c>
       <c r="H11" s="9">
-        <v>0</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>17</v>
+      <c r="J11" s="10">
+        <v>1.57</v>
       </c>
       <c r="K11" s="9">
-        <v>1.7299999999999999E-2</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>17</v>
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="L11" s="10">
+        <v>53</v>
       </c>
       <c r="M11" s="9">
-        <v>0</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="9" t="s">
-        <v>17</v>
+      <c r="O11" s="10">
+        <v>1.57</v>
       </c>
       <c r="P11" s="9">
-        <v>1.7299999999999999E-2</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>17</v>
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>30.85</v>
+        <v>29.7</v>
       </c>
       <c r="C12" s="7">
-        <v>29.7</v>
+        <v>30.6</v>
       </c>
       <c r="D12" s="7">
-        <v>34.65</v>
+        <v>33.5</v>
       </c>
       <c r="E12" s="7">
-        <v>28.8</v>
-      </c>
-      <c r="F12" s="8">
-        <v>-1.1499999999999999</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-3.73</v>
+        <v>28.5</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="G12" s="10">
+        <v>3.03</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
       </c>
-      <c r="I12" s="8">
-        <v>-100</v>
+      <c r="I12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>17</v>
@@ -1795,8 +1795,8 @@
       <c r="M12" s="9">
         <v>0</v>
       </c>
-      <c r="N12" s="8">
-        <v>-100</v>
+      <c r="N12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>17</v>
@@ -1810,31 +1810,31 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>29.55</v>
+        <v>30.85</v>
       </c>
       <c r="C13" s="7">
-        <v>30.85</v>
+        <v>29.7</v>
       </c>
       <c r="D13" s="7">
-        <v>33.15</v>
+        <v>34.65</v>
       </c>
       <c r="E13" s="7">
-        <v>27.9</v>
-      </c>
-      <c r="F13" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="G13" s="10">
-        <v>4.4000000000000004</v>
+        <v>28.8</v>
+      </c>
+      <c r="F13" s="8">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="G13" s="8">
+        <v>-3.73</v>
       </c>
       <c r="H13" s="9">
-        <v>1.7299999999999999E-2</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-100</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>17</v>
@@ -1846,10 +1846,10 @@
         <v>17</v>
       </c>
       <c r="M13" s="9">
-        <v>1.7299999999999999E-2</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>-100</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>17</v>
@@ -1863,28 +1863,28 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>27.95</v>
+        <v>29.55</v>
       </c>
       <c r="C14" s="7">
-        <v>29.55</v>
+        <v>30.85</v>
       </c>
       <c r="D14" s="7">
-        <v>30.35</v>
+        <v>33.15</v>
       </c>
       <c r="E14" s="7">
-        <v>26.35</v>
+        <v>27.9</v>
       </c>
       <c r="F14" s="10">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G14" s="10">
-        <v>5.72</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H14" s="9">
-        <v>0</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>17</v>
@@ -1893,13 +1893,13 @@
         <v>17</v>
       </c>
       <c r="K14" s="9">
-        <v>0</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M14" s="9">
-        <v>0</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>17</v>
@@ -1908,7 +1908,7 @@
         <v>17</v>
       </c>
       <c r="P14" s="9">
-        <v>0</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="Q14" s="9" t="s">
         <v>17</v>
@@ -1916,25 +1916,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>27.75</v>
+        <v>27.95</v>
       </c>
       <c r="C15" s="7">
-        <v>27.95</v>
+        <v>29.55</v>
       </c>
       <c r="D15" s="7">
-        <v>30.05</v>
+        <v>30.35</v>
       </c>
       <c r="E15" s="7">
-        <v>26.25</v>
+        <v>26.35</v>
       </c>
       <c r="F15" s="10">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="G15" s="10">
-        <v>0.72</v>
+        <v>5.72</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1969,25 +1969,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>29.5</v>
+        <v>27.75</v>
       </c>
       <c r="C16" s="7">
-        <v>27.75</v>
+        <v>27.95</v>
       </c>
       <c r="D16" s="7">
-        <v>30.5</v>
+        <v>30.05</v>
       </c>
       <c r="E16" s="7">
-        <v>26.65</v>
-      </c>
-      <c r="F16" s="8">
-        <v>-1.75</v>
-      </c>
-      <c r="G16" s="8">
-        <v>-5.93</v>
+        <v>26.25</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.72</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2022,25 +2022,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="C17" s="7">
-        <v>29.5</v>
+        <v>27.75</v>
       </c>
       <c r="D17" s="7">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
       <c r="E17" s="7">
-        <v>26.45</v>
+        <v>26.65</v>
       </c>
       <c r="F17" s="8">
-        <v>-0.5</v>
+        <v>-1.75</v>
       </c>
       <c r="G17" s="8">
-        <v>-1.67</v>
+        <v>-5.93</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2075,25 +2075,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>28.75</v>
+        <v>30</v>
       </c>
       <c r="C18" s="7">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="D18" s="7">
-        <v>37</v>
+        <v>31.8</v>
       </c>
       <c r="E18" s="7">
-        <v>28.35</v>
-      </c>
-      <c r="F18" s="10">
-        <v>1.25</v>
-      </c>
-      <c r="G18" s="10">
-        <v>4.3499999999999996</v>
+        <v>26.45</v>
+      </c>
+      <c r="F18" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-1.67</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2128,25 +2128,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>27.6</v>
+        <v>28.75</v>
       </c>
       <c r="C19" s="7">
-        <v>28.75</v>
+        <v>30</v>
       </c>
       <c r="D19" s="7">
-        <v>30.15</v>
+        <v>37</v>
       </c>
       <c r="E19" s="7">
-        <v>26.85</v>
+        <v>28.35</v>
       </c>
       <c r="F19" s="10">
-        <v>1.1499999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="G19" s="10">
-        <v>4.17</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2181,25 +2181,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="C20" s="7">
-        <v>27.6</v>
+        <v>28.75</v>
       </c>
       <c r="D20" s="7">
-        <v>29.55</v>
+        <v>30.15</v>
       </c>
       <c r="E20" s="7">
-        <v>25.25</v>
+        <v>26.85</v>
       </c>
       <c r="F20" s="10">
-        <v>0.6</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G20" s="10">
-        <v>2.2200000000000002</v>
+        <v>4.17</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2234,31 +2234,31 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>28.9</v>
+        <v>27</v>
       </c>
       <c r="C21" s="7">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="D21" s="7">
-        <v>29.35</v>
+        <v>29.55</v>
       </c>
       <c r="E21" s="7">
-        <v>26.9</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-6.57</v>
+        <v>25.25</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G21" s="10">
+        <v>2.2200000000000002</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
       </c>
-      <c r="I21" s="8">
-        <v>-100</v>
+      <c r="I21" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>17</v>
@@ -2272,8 +2272,8 @@
       <c r="M21" s="9">
         <v>0</v>
       </c>
-      <c r="N21" s="8">
-        <v>-100</v>
+      <c r="N21" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>17</v>
@@ -2287,146 +2287,146 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>25.5</v>
+        <v>28.9</v>
       </c>
       <c r="C22" s="7">
-        <v>28.9</v>
+        <v>27</v>
       </c>
       <c r="D22" s="7">
-        <v>31.15</v>
+        <v>29.35</v>
       </c>
       <c r="E22" s="7">
-        <v>24.9</v>
-      </c>
-      <c r="F22" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="G22" s="10">
-        <v>13.33</v>
+        <v>26.9</v>
+      </c>
+      <c r="F22" s="8">
+        <v>-1.9</v>
+      </c>
+      <c r="G22" s="8">
+        <v>-6.57</v>
       </c>
       <c r="H22" s="9">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="10">
-        <v>110.6</v>
+        <v>0</v>
+      </c>
+      <c r="I22" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="L22" s="10">
-        <v>6.43</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M22" s="9">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O22" s="10">
-        <v>110.6</v>
+        <v>0</v>
+      </c>
+      <c r="N22" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>6.43</v>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>21.5</v>
+        <v>25.5</v>
       </c>
       <c r="C23" s="7">
-        <v>25.5</v>
+        <v>28.9</v>
       </c>
       <c r="D23" s="7">
-        <v>30.5</v>
+        <v>31.15</v>
       </c>
       <c r="E23" s="7">
-        <v>20.85</v>
+        <v>24.9</v>
       </c>
       <c r="F23" s="10">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G23" s="10">
-        <v>18.600000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="H23" s="9">
-        <v>0</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J23" s="8">
-        <v>-100</v>
+      <c r="J23" s="10">
+        <v>110.6</v>
       </c>
       <c r="K23" s="9">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8">
-        <v>-100</v>
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="L23" s="10">
+        <v>6.43</v>
       </c>
       <c r="M23" s="9">
-        <v>0</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O23" s="8">
-        <v>-100</v>
+      <c r="O23" s="10">
+        <v>110.6</v>
       </c>
       <c r="P23" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>-100</v>
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>6.43</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>19.55</v>
+        <v>21.5</v>
       </c>
       <c r="C24" s="7">
-        <v>21.5</v>
+        <v>25.5</v>
       </c>
       <c r="D24" s="7">
-        <v>23.7</v>
+        <v>30.5</v>
       </c>
       <c r="E24" s="7">
+        <v>20.85</v>
+      </c>
+      <c r="F24" s="10">
+        <v>4</v>
+      </c>
+      <c r="G24" s="10">
         <v>18.600000000000001</v>
       </c>
-      <c r="F24" s="10">
-        <v>1.95</v>
-      </c>
-      <c r="G24" s="10">
-        <v>9.9700000000000006</v>
-      </c>
       <c r="H24" s="9">
         <v>0</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>17</v>
+      <c r="J24" s="8">
+        <v>-100</v>
       </c>
       <c r="K24" s="9">
         <v>0</v>
       </c>
-      <c r="L24" s="9" t="s">
-        <v>17</v>
+      <c r="L24" s="8">
+        <v>-100</v>
       </c>
       <c r="M24" s="9">
         <v>0</v>
@@ -2434,37 +2434,37 @@
       <c r="N24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O24" s="9" t="s">
-        <v>17</v>
+      <c r="O24" s="8">
+        <v>-100</v>
       </c>
       <c r="P24" s="9">
         <v>0</v>
       </c>
-      <c r="Q24" s="9" t="s">
-        <v>17</v>
+      <c r="Q24" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>22.55</v>
+        <v>19.55</v>
       </c>
       <c r="C25" s="7">
-        <v>19.55</v>
+        <v>21.5</v>
       </c>
       <c r="D25" s="7">
-        <v>22.55</v>
+        <v>23.7</v>
       </c>
       <c r="E25" s="7">
-        <v>18.5</v>
-      </c>
-      <c r="F25" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G25" s="8">
-        <v>-13.3</v>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F25" s="10">
+        <v>1.95</v>
+      </c>
+      <c r="G25" s="10">
+        <v>9.9700000000000006</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2499,25 +2499,25 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>22.25</v>
+        <v>22.55</v>
       </c>
       <c r="C26" s="7">
+        <v>19.55</v>
+      </c>
+      <c r="D26" s="7">
         <v>22.55</v>
       </c>
-      <c r="D26" s="7">
-        <v>23.3</v>
-      </c>
       <c r="E26" s="7">
-        <v>19.649999999999999</v>
-      </c>
-      <c r="F26" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G26" s="10">
-        <v>1.35</v>
+        <v>18.5</v>
+      </c>
+      <c r="F26" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G26" s="8">
+        <v>-13.3</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2552,25 +2552,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>19.8</v>
+        <v>22.25</v>
       </c>
       <c r="C27" s="7">
-        <v>22.25</v>
+        <v>22.55</v>
       </c>
       <c r="D27" s="7">
-        <v>46.25</v>
+        <v>23.3</v>
       </c>
       <c r="E27" s="7">
-        <v>19.45</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="F27" s="10">
-        <v>2.4500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="10">
-        <v>12.37</v>
+        <v>1.35</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2605,25 +2605,25 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="C28" s="7">
-        <v>19.8</v>
+        <v>22.25</v>
       </c>
       <c r="D28" s="7">
-        <v>21.4</v>
+        <v>46.25</v>
       </c>
       <c r="E28" s="7">
-        <v>18.399999999999999</v>
+        <v>19.45</v>
       </c>
       <c r="F28" s="10">
-        <v>0.3</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G28" s="10">
-        <v>1.54</v>
+        <v>12.37</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2658,25 +2658,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="C29" s="7">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="D29" s="7">
-        <v>25.95</v>
+        <v>21.4</v>
       </c>
       <c r="E29" s="7">
-        <v>16.45</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="F29" s="10">
-        <v>2.2999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="G29" s="10">
-        <v>13.37</v>
+        <v>1.54</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2711,25 +2711,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
       <c r="C30" s="7">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="D30" s="7">
-        <v>18</v>
+        <v>25.95</v>
       </c>
       <c r="E30" s="7">
-        <v>15.2</v>
+        <v>16.45</v>
       </c>
       <c r="F30" s="10">
-        <v>2</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G30" s="10">
-        <v>13.16</v>
+        <v>13.37</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2764,25 +2764,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>19.04</v>
+        <v>15.2</v>
       </c>
       <c r="C31" s="7">
+        <v>17.2</v>
+      </c>
+      <c r="D31" s="7">
+        <v>18</v>
+      </c>
+      <c r="E31" s="7">
         <v>15.2</v>
       </c>
-      <c r="D31" s="7">
-        <v>19.04</v>
-      </c>
-      <c r="E31" s="7">
-        <v>12.86</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-3.84</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-20.170000000000002</v>
+      <c r="F31" s="10">
+        <v>2</v>
+      </c>
+      <c r="G31" s="10">
+        <v>13.16</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2817,25 +2817,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>18.93</v>
+        <v>19.04</v>
       </c>
       <c r="C32" s="7">
-        <v>19.04</v>
+        <v>15.2</v>
       </c>
       <c r="D32" s="7">
         <v>19.04</v>
       </c>
       <c r="E32" s="7">
-        <v>17.2</v>
-      </c>
-      <c r="F32" s="10">
-        <v>0.11</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0.57999999999999996</v>
+        <v>12.86</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-3.84</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-20.170000000000002</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2870,31 +2870,31 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>19.25</v>
+        <v>18.93</v>
       </c>
       <c r="C33" s="7">
-        <v>18.93</v>
+        <v>19.04</v>
       </c>
       <c r="D33" s="7">
-        <v>19.989999999999998</v>
+        <v>19.04</v>
       </c>
       <c r="E33" s="7">
-        <v>18.010000000000002</v>
-      </c>
-      <c r="F33" s="8">
-        <v>-0.32</v>
-      </c>
-      <c r="G33" s="8">
-        <v>-1.66</v>
+        <v>17.2</v>
+      </c>
+      <c r="F33" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0.57999999999999996</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
       </c>
-      <c r="I33" s="8">
-        <v>-100</v>
+      <c r="I33" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>17</v>
@@ -2908,8 +2908,8 @@
       <c r="M33" s="9">
         <v>0</v>
       </c>
-      <c r="N33" s="8">
-        <v>-100</v>
+      <c r="N33" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>17</v>
@@ -2923,184 +2923,184 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>20.91</v>
+        <v>19.25</v>
       </c>
       <c r="C34" s="7">
-        <v>19.25</v>
+        <v>18.93</v>
       </c>
       <c r="D34" s="7">
-        <v>21.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="E34" s="7">
-        <v>18.21</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="F34" s="8">
+        <v>-0.32</v>
+      </c>
+      <c r="G34" s="8">
         <v>-1.66</v>
       </c>
-      <c r="G34" s="8">
-        <v>-7.94</v>
-      </c>
       <c r="H34" s="9">
-        <v>1.6E-2</v>
-      </c>
-      <c r="I34" s="10">
-        <v>2.17</v>
+        <v>0</v>
+      </c>
+      <c r="I34" s="8">
+        <v>-100</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K34" s="9">
-        <v>3.1600000000000003E-2</v>
-      </c>
-      <c r="L34" s="10">
-        <v>110.2</v>
+        <v>0</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M34" s="9">
-        <v>1.6E-2</v>
-      </c>
-      <c r="N34" s="10">
-        <v>2.17</v>
+        <v>0</v>
+      </c>
+      <c r="N34" s="8">
+        <v>-100</v>
       </c>
       <c r="O34" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P34" s="9">
-        <v>3.1600000000000003E-2</v>
-      </c>
-      <c r="Q34" s="10">
-        <v>110.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>17</v>
+        <v>20.91</v>
       </c>
       <c r="C35" s="7">
-        <v>20.91</v>
+        <v>19.25</v>
       </c>
       <c r="D35" s="7">
-        <v>22.79</v>
+        <v>21.99</v>
       </c>
       <c r="E35" s="7">
-        <v>16.41</v>
-      </c>
-      <c r="F35" s="10">
-        <v>3.91</v>
-      </c>
-      <c r="G35" s="10">
-        <v>23</v>
+        <v>18.21</v>
+      </c>
+      <c r="F35" s="8">
+        <v>-1.66</v>
+      </c>
+      <c r="G35" s="8">
+        <v>-7.94</v>
       </c>
       <c r="H35" s="9">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>17</v>
+        <v>1.6E-2</v>
+      </c>
+      <c r="I35" s="10">
+        <v>2.17</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K35" s="9">
-        <v>1.5599999999999999E-2</v>
+        <v>3.1600000000000003E-2</v>
       </c>
       <c r="L35" s="10">
-        <v>3.99</v>
+        <v>110.2</v>
       </c>
       <c r="M35" s="9">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>17</v>
+        <v>1.6E-2</v>
+      </c>
+      <c r="N35" s="10">
+        <v>2.17</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P35" s="9">
-        <v>1.5599999999999999E-2</v>
+        <v>3.1600000000000003E-2</v>
       </c>
       <c r="Q35" s="10">
-        <v>3.99</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>18.489999999999998</v>
+        <v>17</v>
       </c>
       <c r="C36" s="7">
-        <v>17</v>
+        <v>20.91</v>
       </c>
       <c r="D36" s="7">
-        <v>18.79</v>
+        <v>22.79</v>
       </c>
       <c r="E36" s="7">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="F36" s="8">
-        <v>-1.49</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-8.06</v>
+        <v>16.41</v>
+      </c>
+      <c r="F36" s="10">
+        <v>3.91</v>
+      </c>
+      <c r="G36" s="10">
+        <v>23</v>
       </c>
       <c r="H36" s="9">
-        <v>0</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="8">
-        <v>-100</v>
+      <c r="J36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K36" s="9">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8">
-        <v>-100</v>
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="L36" s="10">
+        <v>3.99</v>
       </c>
       <c r="M36" s="9">
-        <v>0</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O36" s="8">
-        <v>-100</v>
+      <c r="O36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P36" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>-100</v>
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>3.99</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>18</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="C37" s="7">
-        <v>18.489999999999998</v>
+        <v>17</v>
       </c>
       <c r="D37" s="7">
-        <v>19.09</v>
+        <v>18.79</v>
       </c>
       <c r="E37" s="7">
-        <v>18.04</v>
-      </c>
-      <c r="F37" s="10">
-        <v>0.49</v>
-      </c>
-      <c r="G37" s="10">
-        <v>2.72</v>
+        <v>16.059999999999999</v>
+      </c>
+      <c r="F37" s="8">
+        <v>-1.49</v>
+      </c>
+      <c r="G37" s="8">
+        <v>-8.06</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3108,14 +3108,14 @@
       <c r="I37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="9" t="s">
-        <v>17</v>
+      <c r="J37" s="8">
+        <v>-100</v>
       </c>
       <c r="K37" s="9">
         <v>0</v>
       </c>
-      <c r="L37" s="9" t="s">
-        <v>17</v>
+      <c r="L37" s="8">
+        <v>-100</v>
       </c>
       <c r="M37" s="9">
         <v>0</v>
@@ -3123,37 +3123,37 @@
       <c r="N37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>17</v>
+      <c r="O37" s="8">
+        <v>-100</v>
       </c>
       <c r="P37" s="9">
         <v>0</v>
       </c>
-      <c r="Q37" s="9" t="s">
-        <v>17</v>
+      <c r="Q37" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>19.39</v>
+        <v>18</v>
       </c>
       <c r="C38" s="7">
-        <v>18</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="D38" s="7">
-        <v>19.39</v>
+        <v>19.09</v>
       </c>
       <c r="E38" s="7">
-        <v>17.5</v>
-      </c>
-      <c r="F38" s="8">
-        <v>-1.39</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-7.17</v>
+        <v>18.04</v>
+      </c>
+      <c r="F38" s="10">
+        <v>0.49</v>
+      </c>
+      <c r="G38" s="10">
+        <v>2.72</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3188,25 +3188,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>19.7</v>
+        <v>19.39</v>
       </c>
       <c r="C39" s="7">
+        <v>18</v>
+      </c>
+      <c r="D39" s="7">
         <v>19.39</v>
       </c>
-      <c r="D39" s="7">
-        <v>20.190000000000001</v>
-      </c>
       <c r="E39" s="7">
-        <v>18.440000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="F39" s="8">
-        <v>-0.31</v>
+        <v>-1.39</v>
       </c>
       <c r="G39" s="8">
-        <v>-1.57</v>
+        <v>-7.17</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3241,25 +3241,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="C40" s="7">
+        <v>19.39</v>
+      </c>
+      <c r="D40" s="7">
         <v>20.190000000000001</v>
       </c>
-      <c r="C40" s="7">
-        <v>19.7</v>
-      </c>
-      <c r="D40" s="7">
-        <v>20.2</v>
-      </c>
       <c r="E40" s="7">
-        <v>19.3</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="F40" s="8">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="G40" s="8">
-        <v>-2.4300000000000002</v>
+        <v>-1.57</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3294,25 +3294,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="C41" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="D41" s="7">
         <v>20.2</v>
       </c>
-      <c r="C41" s="7">
-        <v>20.190000000000001</v>
-      </c>
-      <c r="D41" s="7">
-        <v>20.99</v>
-      </c>
       <c r="E41" s="7">
-        <v>19.11</v>
+        <v>19.3</v>
       </c>
       <c r="F41" s="8">
-        <v>-0.01</v>
+        <v>-0.49</v>
       </c>
       <c r="G41" s="8">
-        <v>-0.05</v>
+        <v>-2.4300000000000002</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3347,25 +3347,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>20.29</v>
+        <v>20.2</v>
       </c>
       <c r="C42" s="7">
-        <v>20.2</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="D42" s="7">
-        <v>21.99</v>
+        <v>20.99</v>
       </c>
       <c r="E42" s="7">
-        <v>19.3</v>
+        <v>19.11</v>
       </c>
       <c r="F42" s="8">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="G42" s="8">
-        <v>-0.44</v>
+        <v>-0.05</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3400,25 +3400,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>19.98</v>
+        <v>20.29</v>
       </c>
       <c r="C43" s="7">
-        <v>20.29</v>
+        <v>20.2</v>
       </c>
       <c r="D43" s="7">
-        <v>20.62</v>
+        <v>21.99</v>
       </c>
       <c r="E43" s="7">
-        <v>19.2</v>
-      </c>
-      <c r="F43" s="10">
-        <v>0.31</v>
-      </c>
-      <c r="G43" s="10">
-        <v>1.55</v>
+        <v>19.3</v>
+      </c>
+      <c r="F43" s="8">
+        <v>-0.09</v>
+      </c>
+      <c r="G43" s="8">
+        <v>-0.44</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3453,25 +3453,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>20.3</v>
+        <v>19.98</v>
       </c>
       <c r="C44" s="7">
-        <v>19.98</v>
+        <v>20.29</v>
       </c>
       <c r="D44" s="7">
-        <v>21.04</v>
+        <v>20.62</v>
       </c>
       <c r="E44" s="7">
         <v>19.2</v>
       </c>
-      <c r="F44" s="8">
-        <v>-0.32</v>
-      </c>
-      <c r="G44" s="8">
-        <v>-1.58</v>
+      <c r="F44" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="G44" s="10">
+        <v>1.55</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3506,25 +3506,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
+        <v>20.3</v>
+      </c>
+      <c r="C45" s="7">
+        <v>19.98</v>
+      </c>
+      <c r="D45" s="7">
         <v>21.04</v>
-      </c>
-      <c r="C45" s="7">
-        <v>20.3</v>
-      </c>
-      <c r="D45" s="7">
-        <v>21.7</v>
       </c>
       <c r="E45" s="7">
         <v>19.2</v>
       </c>
       <c r="F45" s="8">
-        <v>-0.74</v>
+        <v>-0.32</v>
       </c>
       <c r="G45" s="8">
-        <v>-3.52</v>
+        <v>-1.58</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3559,25 +3559,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>21.99</v>
+        <v>21.04</v>
       </c>
       <c r="C46" s="7">
-        <v>21.04</v>
+        <v>20.3</v>
       </c>
       <c r="D46" s="7">
-        <v>21.89</v>
+        <v>21.7</v>
       </c>
       <c r="E46" s="7">
-        <v>19.489999999999998</v>
+        <v>19.2</v>
       </c>
       <c r="F46" s="8">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="G46" s="8">
-        <v>-4.32</v>
+        <v>-3.52</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>17</v>
@@ -3604,7 +3604,7 @@
         <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="9" t="s">
         <v>17</v>
@@ -3612,31 +3612,31 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>19.600000000000001</v>
+        <v>21.99</v>
       </c>
       <c r="C47" s="7">
-        <v>21.99</v>
+        <v>21.04</v>
       </c>
       <c r="D47" s="7">
-        <v>23.14</v>
+        <v>21.89</v>
       </c>
       <c r="E47" s="7">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="F47" s="10">
-        <v>2.39</v>
-      </c>
-      <c r="G47" s="10">
-        <v>12.19</v>
+        <v>19.489999999999998</v>
+      </c>
+      <c r="F47" s="8">
+        <v>-0.95</v>
+      </c>
+      <c r="G47" s="8">
+        <v>-4.32</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
       </c>
-      <c r="I47" s="8">
-        <v>-100</v>
+      <c r="I47" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>17</v>
@@ -3650,8 +3650,8 @@
       <c r="M47" s="9">
         <v>0</v>
       </c>
-      <c r="N47" s="8">
-        <v>-100</v>
+      <c r="N47" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>17</v>
@@ -3665,31 +3665,31 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>20.53</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="C48" s="7">
-        <v>19.600000000000001</v>
+        <v>21.99</v>
       </c>
       <c r="D48" s="7">
-        <v>21.89</v>
+        <v>23.14</v>
       </c>
       <c r="E48" s="7">
-        <v>19</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-0.93</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-4.53</v>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F48" s="10">
+        <v>2.39</v>
+      </c>
+      <c r="G48" s="10">
+        <v>12.19</v>
       </c>
       <c r="H48" s="9">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I48" s="8">
+        <v>-100</v>
       </c>
       <c r="J48" s="9" t="s">
         <v>17</v>
@@ -3701,10 +3701,10 @@
         <v>17</v>
       </c>
       <c r="M48" s="9">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N48" s="8">
+        <v>-100</v>
       </c>
       <c r="O48" s="9" t="s">
         <v>17</v>
@@ -3718,28 +3718,28 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>21.02</v>
+        <v>20.53</v>
       </c>
       <c r="C49" s="7">
-        <v>20.53</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="D49" s="7">
-        <v>22.09</v>
+        <v>21.89</v>
       </c>
       <c r="E49" s="7">
-        <v>20.14</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8">
-        <v>-0.49</v>
+        <v>-0.93</v>
       </c>
       <c r="G49" s="8">
-        <v>-2.33</v>
+        <v>-4.53</v>
       </c>
       <c r="H49" s="9">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>17</v>
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="K49" s="9">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M49" s="9">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>17</v>
@@ -3763,7 +3763,7 @@
         <v>17</v>
       </c>
       <c r="P49" s="9">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q49" s="9" t="s">
         <v>17</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>22.99</v>
+        <v>21.02</v>
       </c>
       <c r="C50" s="7">
-        <v>21.02</v>
+        <v>20.53</v>
       </c>
       <c r="D50" s="7">
-        <v>23.49</v>
+        <v>22.09</v>
       </c>
       <c r="E50" s="7">
-        <v>20.010000000000002</v>
+        <v>20.14</v>
       </c>
       <c r="F50" s="8">
-        <v>-1.97</v>
+        <v>-0.49</v>
       </c>
       <c r="G50" s="8">
-        <v>-8.57</v>
+        <v>-2.33</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3824,25 +3824,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>22.91</v>
+        <v>22.99</v>
       </c>
       <c r="C51" s="7">
-        <v>22.99</v>
+        <v>21.02</v>
       </c>
       <c r="D51" s="7">
-        <v>24.1</v>
+        <v>23.49</v>
       </c>
       <c r="E51" s="7">
-        <v>22.04</v>
-      </c>
-      <c r="F51" s="10">
-        <v>0.08</v>
-      </c>
-      <c r="G51" s="10">
-        <v>0.35</v>
+        <v>20.010000000000002</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-1.97</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-8.57</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3877,25 +3877,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
-        <v>24.28</v>
+        <v>22.91</v>
       </c>
       <c r="C52" s="7">
-        <v>22.91</v>
+        <v>22.99</v>
       </c>
       <c r="D52" s="7">
-        <v>24.69</v>
+        <v>24.1</v>
       </c>
       <c r="E52" s="7">
-        <v>22.82</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-1.37</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-5.64</v>
+        <v>22.04</v>
+      </c>
+      <c r="F52" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="G52" s="10">
+        <v>0.35</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3930,25 +3930,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>25.4</v>
+        <v>24.28</v>
       </c>
       <c r="C53" s="7">
-        <v>24.28</v>
+        <v>22.91</v>
       </c>
       <c r="D53" s="7">
-        <v>25.78</v>
+        <v>24.69</v>
       </c>
       <c r="E53" s="7">
-        <v>23.4</v>
+        <v>22.82</v>
       </c>
       <c r="F53" s="8">
-        <v>-1.1200000000000001</v>
+        <v>-1.37</v>
       </c>
       <c r="G53" s="8">
-        <v>-4.41</v>
+        <v>-5.64</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3983,25 +3983,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>24.92</v>
+        <v>25.4</v>
       </c>
       <c r="C54" s="7">
-        <v>25.4</v>
+        <v>24.28</v>
       </c>
       <c r="D54" s="7">
-        <v>26.62</v>
+        <v>25.78</v>
       </c>
       <c r="E54" s="7">
-        <v>24.91</v>
-      </c>
-      <c r="F54" s="10">
-        <v>0.48</v>
-      </c>
-      <c r="G54" s="10">
-        <v>1.93</v>
+        <v>23.4</v>
+      </c>
+      <c r="F54" s="8">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="G54" s="8">
+        <v>-4.41</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4036,25 +4036,25 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
-        <v>24.99</v>
+        <v>24.92</v>
       </c>
       <c r="C55" s="7">
-        <v>24.92</v>
+        <v>25.4</v>
       </c>
       <c r="D55" s="7">
-        <v>26.5</v>
+        <v>26.62</v>
       </c>
       <c r="E55" s="7">
-        <v>23.01</v>
-      </c>
-      <c r="F55" s="8">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-      <c r="G55" s="8">
-        <v>-0.28000000000000003</v>
+        <v>24.91</v>
+      </c>
+      <c r="F55" s="10">
+        <v>0.48</v>
+      </c>
+      <c r="G55" s="10">
+        <v>1.93</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -4089,25 +4089,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>24.71</v>
+        <v>24.99</v>
       </c>
       <c r="C56" s="7">
-        <v>24.99</v>
+        <v>24.92</v>
       </c>
       <c r="D56" s="7">
-        <v>25.4</v>
+        <v>26.5</v>
       </c>
       <c r="E56" s="7">
-        <v>21.2</v>
-      </c>
-      <c r="F56" s="10">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G56" s="10">
-        <v>1.1299999999999999</v>
+        <v>23.01</v>
+      </c>
+      <c r="F56" s="8">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="G56" s="8">
+        <v>-0.28000000000000003</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4142,25 +4142,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
-        <v>23.99</v>
+        <v>24.71</v>
       </c>
       <c r="C57" s="7">
-        <v>24.71</v>
+        <v>24.99</v>
       </c>
       <c r="D57" s="7">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="E57" s="7">
-        <v>21.01</v>
+        <v>21.2</v>
       </c>
       <c r="F57" s="10">
-        <v>0.72</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G57" s="10">
-        <v>3</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4195,25 +4195,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
-        <v>29.19</v>
+        <v>23.99</v>
       </c>
       <c r="C58" s="7">
-        <v>23.99</v>
+        <v>24.71</v>
       </c>
       <c r="D58" s="7">
-        <v>30.3</v>
+        <v>28.2</v>
       </c>
       <c r="E58" s="7">
-        <v>21.31</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-5.2</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-17.809999999999999</v>
+        <v>21.01</v>
+      </c>
+      <c r="F58" s="10">
+        <v>0.72</v>
+      </c>
+      <c r="G58" s="10">
+        <v>3</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4248,25 +4248,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>19.8</v>
+        <v>29.19</v>
       </c>
       <c r="C59" s="7">
-        <v>29.19</v>
+        <v>23.99</v>
       </c>
       <c r="D59" s="7">
-        <v>38.090000000000003</v>
+        <v>30.3</v>
       </c>
       <c r="E59" s="7">
-        <v>19.8</v>
-      </c>
-      <c r="F59" s="10">
-        <v>9.39</v>
-      </c>
-      <c r="G59" s="10">
-        <v>47.42</v>
+        <v>21.31</v>
+      </c>
+      <c r="F59" s="8">
+        <v>-5.2</v>
+      </c>
+      <c r="G59" s="8">
+        <v>-17.809999999999999</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4301,25 +4301,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
-        <v>18.309999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="C60" s="7">
+        <v>29.19</v>
+      </c>
+      <c r="D60" s="7">
+        <v>38.090000000000003</v>
+      </c>
+      <c r="E60" s="7">
         <v>19.8</v>
       </c>
-      <c r="D60" s="7">
-        <v>20.09</v>
-      </c>
-      <c r="E60" s="7">
-        <v>17.11</v>
-      </c>
       <c r="F60" s="10">
-        <v>1.49</v>
+        <v>9.39</v>
       </c>
       <c r="G60" s="10">
-        <v>8.14</v>
+        <v>47.42</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4354,25 +4354,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7">
-        <v>23.81</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="C61" s="7">
-        <v>18.309999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="D61" s="7">
-        <v>23.8</v>
+        <v>20.09</v>
       </c>
       <c r="E61" s="7">
-        <v>17.59</v>
-      </c>
-      <c r="F61" s="8">
-        <v>-5.5</v>
-      </c>
-      <c r="G61" s="8">
-        <v>-23.1</v>
+        <v>17.11</v>
+      </c>
+      <c r="F61" s="10">
+        <v>1.49</v>
+      </c>
+      <c r="G61" s="10">
+        <v>8.14</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4407,25 +4407,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7">
-        <v>30.05</v>
+        <v>23.81</v>
       </c>
       <c r="C62" s="7">
-        <v>23.81</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="D62" s="7">
-        <v>30.51</v>
+        <v>23.8</v>
       </c>
       <c r="E62" s="7">
-        <v>23.7</v>
+        <v>17.59</v>
       </c>
       <c r="F62" s="8">
-        <v>-6.24</v>
+        <v>-5.5</v>
       </c>
       <c r="G62" s="8">
-        <v>-20.77</v>
+        <v>-23.1</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4460,25 +4460,25 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7">
-        <v>39</v>
+        <v>30.05</v>
       </c>
       <c r="C63" s="7">
-        <v>30.05</v>
+        <v>23.81</v>
       </c>
       <c r="D63" s="7">
-        <v>39.5</v>
+        <v>30.51</v>
       </c>
       <c r="E63" s="7">
-        <v>29.5</v>
+        <v>23.7</v>
       </c>
       <c r="F63" s="8">
-        <v>-8.9499999999999993</v>
+        <v>-6.24</v>
       </c>
       <c r="G63" s="8">
-        <v>-22.95</v>
+        <v>-20.77</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4513,25 +4513,25 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7">
-        <v>48.48</v>
+        <v>39</v>
       </c>
       <c r="C64" s="7">
-        <v>39</v>
+        <v>30.05</v>
       </c>
       <c r="D64" s="7">
-        <v>52.1</v>
+        <v>39.5</v>
       </c>
       <c r="E64" s="7">
-        <v>37.54</v>
+        <v>29.5</v>
       </c>
       <c r="F64" s="8">
-        <v>-10.48</v>
+        <v>-8.9499999999999993</v>
       </c>
       <c r="G64" s="8">
-        <v>-21.18</v>
+        <v>-22.95</v>
       </c>
       <c r="H64" s="9">
         <v>0</v>
@@ -4566,25 +4566,25 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>17</v>
+        <v>42887</v>
+      </c>
+      <c r="B65" s="7">
+        <v>48.48</v>
+      </c>
+      <c r="C65" s="7">
+        <v>39</v>
+      </c>
+      <c r="D65" s="7">
+        <v>52.1</v>
+      </c>
+      <c r="E65" s="7">
+        <v>37.54</v>
+      </c>
+      <c r="F65" s="8">
+        <v>-10.48</v>
+      </c>
+      <c r="G65" s="8">
+        <v>-21.18</v>
       </c>
       <c r="H65" s="9">
         <v>0</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4884,7 +4884,7 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4937,7 +4937,7 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5096,7 +5096,7 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5149,7 +5149,7 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5202,54 +5202,107 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
+        <v>42522</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77" s="9">
+        <v>0</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M77" s="9">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P77" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
         <v>42491</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="9">
-        <v>0</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K77" s="9">
-        <v>0</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M77" s="9">
-        <v>0</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P77" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="9" t="s">
+      <c r="B78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="9">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78" s="9">
+        <v>0</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M78" s="9">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P78" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="9" t="s">
         <v>17</v>
       </c>
     </row>
